--- a/ROUTE_5_PATH5_COE_AIML_CSE_MECH_AUDI/PATH5_ANSWER_KEY.xlsx
+++ b/ROUTE_5_PATH5_COE_AIML_CSE_MECH_AUDI/PATH5_ANSWER_KEY.xlsx
@@ -456,13 +456,13 @@
         <v>Round 1 (R1)</v>
       </c>
       <c r="B3" t="str">
-        <v>COE (LIB)</v>
+        <v>Station 1 (Library)</v>
       </c>
       <c r="C3" t="str">
-        <v>Object Finding (COE Board)</v>
+        <v>Object Finding</v>
       </c>
       <c r="D3" t="str">
-        <v>Find assigned COE Board object, upload photo, enter volunteer code</v>
+        <v>Find assigned object, upload photo, enter volunteer code</v>
       </c>
       <c r="E3" t="str">
         <v>None</v>
@@ -479,28 +479,28 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Round 2 Location Clue</v>
+        <v>Round 2 Location Clues</v>
       </c>
       <c r="B4" t="str">
-        <v>In-App Riddle</v>
+        <v>In-App Riddles</v>
       </c>
       <c r="C4" t="str">
-        <v>Riddle of Missing Concept (A+I+M+L)</v>
+        <v>Missing Concept Riddles (Slide-by-Slide)</v>
       </c>
       <c r="D4" t="str">
-        <v>Algorithm (A) + Internet (I) + Model (M) + Language (L) -&gt; Destination: AIML -&gt; Start Code: AIML-START</v>
+        <v>1. ALGORITHM (A) | 2. INTERNET (I) | 3. MODEL (M) | 4. LANGUAGE (L) -&gt; Deduced: AIML</v>
       </c>
       <c r="E4" t="str">
         <v>None</v>
       </c>
       <c r="F4" t="str">
-        <v>AIML &amp; Start Code: AIML-START (UPPERCASE ONLY)</v>
+        <v>ALGORITHM, INTERNET, MODEL, LANGUAGE -&gt; Destination: AIML (UPPERCASE ONLY)</v>
       </c>
       <c r="G4" t="str">
-        <v>Strict UPPERCASE regex &amp; normalize-space(.) = 'AIML' &amp; 'AIML-START'</v>
+        <v>Strict UPPERCASE regex &amp; normalize-space(.) for all 4 concepts and AIML</v>
       </c>
       <c r="H4" t="str">
-        <v>No (Input Mandatory)</v>
+        <v>No (Inputs Mandatory)</v>
       </c>
     </row>
     <row r="5">
@@ -514,19 +514,19 @@
         <v>Reverse Image Prompting Challenge</v>
       </c>
       <c r="D5" t="str">
-        <v>Recreate 3 slideshow images in 3 different AI chats + Photo + Codes</v>
+        <v>Start Code: GEMMA-V05 -&gt; Recreate 3 slideshow images in 3 AI chats + Photo (1 Mandatory, 1 Optional) -&gt; Final Code: OLLAMA-V05</v>
       </c>
       <c r="E5" t="str">
         <v>None</v>
       </c>
       <c r="F5" t="str">
-        <v>Status: PASSED -&gt; Code 1: GEMMA-V05 -&gt; Finish Code: OLLAMA-V05</v>
+        <v>Start: GEMMA-V05 -&gt; Photo -&gt; Final Code: OLLAMA-V05</v>
       </c>
       <c r="G5" t="str">
-        <v>Status = PASSED &amp; normalize-space(.) = 'GEMMA-V05' &amp; 'OLLAMA-V05'</v>
+        <v>Start Code = 'GEMMA-V05' &amp; Final Code = 'OLLAMA-V05'</v>
       </c>
       <c r="H5" t="str">
-        <v>Yes (Station Photo MANDATORY)</v>
+        <v>Yes (Photo 1 Mandatory, Photo 2 Optional)</v>
       </c>
     </row>
     <row r="6">
@@ -566,7 +566,7 @@
         <v>QR Hunt</v>
       </c>
       <c r="D7" t="str">
-        <v>Scan hidden QR code in CSE, upload photo</v>
+        <v>Scan hidden QR code in CSE</v>
       </c>
       <c r="E7" t="str">
         <v>None</v>
@@ -578,7 +578,7 @@
         <v>Scanned barcode = 'PETER_PARKER'</v>
       </c>
       <c r="H7" t="str">
-        <v>Yes (Barcode Scan &amp; Photo MANDATORY)</v>
+        <v>Yes (Barcode Scan MANDATORY)</v>
       </c>
     </row>
     <row r="8">
@@ -589,22 +589,22 @@
         <v>In-App Image (badminton court.jpeg)</v>
       </c>
       <c r="C8" t="str">
-        <v>MEC-02 Piece-by-Piece</v>
+        <v>Piece-by-Piece Clue</v>
       </c>
       <c r="D8" t="str">
-        <v>Identify location from photograph pieces -&gt; Destination: MECH -&gt; Start Code: PIECE-START</v>
+        <v>Identify location from photograph pieces -&gt; Destination: MECH</v>
       </c>
       <c r="E8" t="str">
         <v>badminton court.jpeg</v>
       </c>
       <c r="F8" t="str">
-        <v>MECH &amp; Start Code: PIECE-START (UPPERCASE ONLY)</v>
+        <v>MECH (UPPERCASE ONLY)</v>
       </c>
       <c r="G8" t="str">
-        <v>Strict UPPERCASE regex &amp; normalize-space(.) = 'MECH' &amp; 'PIECE-START'</v>
+        <v>Strict UPPERCASE regex &amp; normalize-space(.) = 'MECH'</v>
       </c>
       <c r="H8" t="str">
-        <v>No (Inputs Mandatory)</v>
+        <v>No (Input Mandatory)</v>
       </c>
     </row>
     <row r="9">
@@ -618,16 +618,16 @@
         <v>Physical Challenge</v>
       </c>
       <c r="D9" t="str">
-        <v>Complete physical challenge with volunteer, select PASSED, upload photo, enter finish code PIECE-BYE</v>
+        <v>Enter Start Code: PIECE-START, complete physical challenge, upload photo, enter End Code: PIECE-BYE</v>
       </c>
       <c r="E9" t="str">
         <v>None</v>
       </c>
       <c r="F9" t="str">
-        <v>Status: PASSED, Finish Code: PIECE-BYE (UPPERCASE ONLY)</v>
+        <v>Start: PIECE-START -&gt; Photo -&gt; End Code: PIECE-BYE (UPPERCASE ONLY)</v>
       </c>
       <c r="G9" t="str">
-        <v>Status = PASSED &amp; normalize-space(.) = 'PIECE-BYE'</v>
+        <v>normalize-space(.) = 'PIECE-START' &amp; 'PIECE-BYE'</v>
       </c>
       <c r="H9" t="str">
         <v>Yes (Challenge Photo MANDATORY)</v>
@@ -635,13 +635,13 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Final Round (Riddle 1)</v>
+        <v>Round 5 (Riddle 1)</v>
       </c>
       <c r="B10" t="str">
         <v>Main Auditorium</v>
       </c>
       <c r="C10" t="str">
-        <v>Auditorium Riddle</v>
+        <v>Riddle 1</v>
       </c>
       <c r="D10" t="str">
         <v>Solve riddle: Empty yet built for crowds, seats not meant to sleep...</v>
@@ -661,13 +661,13 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Final Round (Riddle 2)</v>
+        <v>Round 5 (Riddle 2)</v>
       </c>
       <c r="B11" t="str">
         <v>Main Auditorium Stage</v>
       </c>
       <c r="C11" t="str">
-        <v>Stage Riddle</v>
+        <v>Riddle 2</v>
       </c>
       <c r="D11" t="str">
         <v>Solve stage riddle: Elevated above crowd, wooden floor...</v>
